--- a/功能清单.xlsx
+++ b/功能清单.xlsx
@@ -26,10 +26,6 @@
 </workbook>
 </file>
 
-<file path=xl/cellimages.xml><?xml version="1.0" encoding="utf-8"?>
-<etc:cellImages xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData"/>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="317">
   <si>
@@ -90,6 +86,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
       <t>根据业务需求制定数据字典，可在</t>
     </r>
     <r>
@@ -115,6 +116,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">在数据资产-数据资产管理-数据标签管理页面，点击新增按钮。
 在新增标签弹窗中配置标签名称、识别规则和描述。（正则表达式）
 </t>
@@ -1186,7 +1192,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="31">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -1228,6 +1234,19 @@
     <font>
       <b/>
       <sz val="12"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="0"/>
       <name val="等线"/>
       <charset val="134"/>
     </font>
@@ -1395,7 +1414,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1410,13 +1429,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0"/>
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1731,28 +1756,19 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1761,122 +1777,131 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1919,23 +1944,29 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2464,10 +2495,10 @@
       <c r="D15" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="E15" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="F15" s="9" t="s">
+      <c r="F15" s="15" t="s">
         <v>37</v>
       </c>
     </row>
@@ -2476,8 +2507,8 @@
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="9" t="s">
+      <c r="E16" s="14"/>
+      <c r="F16" s="15" t="s">
         <v>38</v>
       </c>
     </row>
@@ -2486,8 +2517,8 @@
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="14" t="s">
+      <c r="E17" s="14"/>
+      <c r="F17" s="15" t="s">
         <v>39</v>
       </c>
     </row>
@@ -2496,8 +2527,8 @@
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="14" t="s">
+      <c r="E18" s="14"/>
+      <c r="F18" s="15" t="s">
         <v>40</v>
       </c>
     </row>
@@ -2506,8 +2537,8 @@
       <c r="B19" s="6"/>
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="14" t="s">
+      <c r="E19" s="14"/>
+      <c r="F19" s="15" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2516,10 +2547,10 @@
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
       <c r="D20" s="6"/>
-      <c r="E20" s="15" t="s">
+      <c r="E20" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="F20" s="16" t="s">
+      <c r="F20" s="15" t="s">
         <v>43</v>
       </c>
     </row>
@@ -2528,8 +2559,8 @@
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
       <c r="D21" s="6"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="16" t="s">
+      <c r="E21" s="14"/>
+      <c r="F21" s="15" t="s">
         <v>44</v>
       </c>
     </row>
@@ -2538,8 +2569,8 @@
       <c r="B22" s="6"/>
       <c r="C22" s="6"/>
       <c r="D22" s="6"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="14" t="s">
+      <c r="E22" s="14"/>
+      <c r="F22" s="15" t="s">
         <v>45</v>
       </c>
     </row>
@@ -2548,8 +2579,8 @@
       <c r="B23" s="6"/>
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="14" t="s">
+      <c r="E23" s="14"/>
+      <c r="F23" s="15" t="s">
         <v>46</v>
       </c>
     </row>
@@ -2558,8 +2589,8 @@
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
       <c r="D24" s="6"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="14" t="s">
+      <c r="E24" s="14"/>
+      <c r="F24" s="15" t="s">
         <v>47</v>
       </c>
     </row>
@@ -2568,8 +2599,8 @@
       <c r="B25" s="6"/>
       <c r="C25" s="6"/>
       <c r="D25" s="6"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="16" t="s">
+      <c r="E25" s="14"/>
+      <c r="F25" s="15" t="s">
         <v>48</v>
       </c>
     </row>
@@ -2578,10 +2609,10 @@
       <c r="B26" s="6"/>
       <c r="C26" s="6"/>
       <c r="D26" s="6"/>
-      <c r="E26" s="6" t="s">
+      <c r="E26" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="F26" s="9" t="s">
+      <c r="F26" s="15" t="s">
         <v>50</v>
       </c>
     </row>
@@ -2590,10 +2621,10 @@
       <c r="B27" s="6"/>
       <c r="C27" s="6"/>
       <c r="D27" s="6"/>
-      <c r="E27" s="17" t="s">
+      <c r="E27" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="F27" s="16" t="s">
+      <c r="F27" s="15" t="s">
         <v>52</v>
       </c>
     </row>
@@ -2602,10 +2633,10 @@
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
       <c r="D28" s="6"/>
-      <c r="E28" s="12" t="s">
+      <c r="E28" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="F28" s="13" t="s">
+      <c r="F28" s="17" t="s">
         <v>54</v>
       </c>
     </row>
@@ -3536,10 +3567,10 @@
       <c r="D102" s="6" t="s">
         <v>223</v>
       </c>
-      <c r="E102" s="15" t="s">
+      <c r="E102" s="20" t="s">
         <v>224</v>
       </c>
-      <c r="F102" s="14" t="s">
+      <c r="F102" s="21" t="s">
         <v>225</v>
       </c>
     </row>
@@ -3548,10 +3579,10 @@
       <c r="B103" s="6"/>
       <c r="C103" s="6"/>
       <c r="D103" s="6"/>
-      <c r="E103" s="15" t="s">
+      <c r="E103" s="20" t="s">
         <v>226</v>
       </c>
-      <c r="F103" s="14" t="s">
+      <c r="F103" s="21" t="s">
         <v>227</v>
       </c>
     </row>
@@ -3560,10 +3591,10 @@
       <c r="B104" s="6"/>
       <c r="C104" s="6"/>
       <c r="D104" s="6"/>
-      <c r="E104" s="15" t="s">
+      <c r="E104" s="20" t="s">
         <v>228</v>
       </c>
-      <c r="F104" s="14" t="s">
+      <c r="F104" s="21" t="s">
         <v>229</v>
       </c>
     </row>
@@ -3638,10 +3669,10 @@
       <c r="B110" s="6"/>
       <c r="C110" s="6"/>
       <c r="D110" s="6"/>
-      <c r="E110" s="15" t="s">
+      <c r="E110" s="20" t="s">
         <v>243</v>
       </c>
-      <c r="F110" s="14" t="s">
+      <c r="F110" s="21" t="s">
         <v>244</v>
       </c>
     </row>
@@ -3674,10 +3705,10 @@
       <c r="B113" s="6"/>
       <c r="C113" s="6"/>
       <c r="D113" s="6"/>
-      <c r="E113" s="17" t="s">
+      <c r="E113" s="14" t="s">
         <v>249</v>
       </c>
-      <c r="F113" s="16" t="s">
+      <c r="F113" s="15" t="s">
         <v>250</v>
       </c>
     </row>
@@ -3686,10 +3717,10 @@
       <c r="B114" s="6"/>
       <c r="C114" s="6"/>
       <c r="D114" s="6"/>
-      <c r="E114" s="15" t="s">
+      <c r="E114" s="20" t="s">
         <v>251</v>
       </c>
-      <c r="F114" s="14" t="s">
+      <c r="F114" s="21" t="s">
         <v>252</v>
       </c>
     </row>
@@ -3942,7 +3973,7 @@
       <c r="D134" s="10" t="s">
         <v>298</v>
       </c>
-      <c r="E134" s="20"/>
+      <c r="E134" s="22"/>
       <c r="F134" s="9" t="s">
         <v>299</v>
       </c>
@@ -3954,7 +3985,7 @@
       <c r="D135" s="10" t="s">
         <v>300</v>
       </c>
-      <c r="E135" s="20"/>
+      <c r="E135" s="22"/>
       <c r="F135" s="9" t="s">
         <v>301</v>
       </c>
@@ -3972,7 +4003,7 @@
       <c r="D136" s="6" t="s">
         <v>305</v>
       </c>
-      <c r="E136" s="21" t="s">
+      <c r="E136" s="23" t="s">
         <v>306</v>
       </c>
       <c r="F136" s="9" t="s">
